--- a/spreadsheet/macrofree/appservicewebapps_sg_checklist.es.xlsx
+++ b/spreadsheet/macrofree/appservicewebapps_sg_checklist.es.xlsx
@@ -1738,7 +1738,11 @@
           <t>(Plan de App Service) Valide los cambios de la aplicación en la ranura de ensayo antes de intercambiarla por la ranura de producción.</t>
         </is>
       </c>
-      <c r="D28" s="21" t="n"/>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>Evite el tiempo de inactividad y los errores.  Vuelva rápidamente al último estado bueno conocido si detecta un problema después de un intercambio.</t>
+        </is>
+      </c>
       <c r="E28" s="21" t="n"/>
       <c r="F28" t="inlineStr">
         <is>
